--- a/results/block2_results/area/Normal_2/branches/dataframes/dataset_LCA_B06_Normal_2.xlsx
+++ b/results/block2_results/area/Normal_2/branches/dataframes/dataset_LCA_B06_Normal_2.xlsx
@@ -523,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1865502853357017</v>
+        <v>0.1865600545781031</v>
       </c>
     </row>
     <row r="3">
@@ -564,7 +564,7 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9027069616915873</v>
+        <v>0.9025130183448353</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>1.329790079151363</v>
+        <v>1.329840539349983</v>
       </c>
     </row>
     <row r="5">
@@ -646,7 +646,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45343381859624</v>
+        <v>3.466416537272089</v>
       </c>
     </row>
     <row r="6">
@@ -687,7 +687,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45343381859624</v>
+        <v>3.466416537272089</v>
       </c>
     </row>
     <row r="7">
@@ -728,7 +728,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>5.333486823954726</v>
+        <v>5.331086360382172</v>
       </c>
     </row>
     <row r="8">
@@ -769,7 +769,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>6.042760034830393</v>
+        <v>6.039954809969425</v>
       </c>
     </row>
     <row r="9">
@@ -810,7 +810,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>9.774211633003286</v>
+        <v>9.635797748144768</v>
       </c>
     </row>
     <row r="10">
@@ -851,7 +851,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>10.47404150664014</v>
+        <v>10.47449632497913</v>
       </c>
     </row>
     <row r="11">
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>10.50943319366649</v>
+        <v>10.50475136658863</v>
       </c>
     </row>
     <row r="12">
@@ -933,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>12.00213237476259</v>
+        <v>11.98254064055079</v>
       </c>
     </row>
     <row r="13">
@@ -974,7 +974,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>12.00213237476259</v>
+        <v>11.98254064055079</v>
       </c>
     </row>
     <row r="14">
@@ -1015,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>12.33737930054762</v>
+        <v>12.33786735892068</v>
       </c>
     </row>
     <row r="15">
@@ -1056,7 +1056,7 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>1.112358201660258</v>
+        <v>1.112431640076021</v>
       </c>
     </row>
     <row r="16">
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>1.062777698332418</v>
+        <v>1.063099514135826</v>
       </c>
     </row>
     <row r="17">
@@ -1138,7 +1138,7 @@
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5772589909199825</v>
+        <v>0.5792498871576799</v>
       </c>
     </row>
     <row r="18">
@@ -1179,7 +1179,7 @@
         <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>15.92122532206255</v>
+        <v>16.08614487448754</v>
       </c>
     </row>
     <row r="19">
@@ -1220,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>15.92244207042752</v>
+        <v>15.9224055805709</v>
       </c>
     </row>
     <row r="20">
@@ -1261,7 +1261,7 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>15.90440478338968</v>
+        <v>15.90529663782263</v>
       </c>
     </row>
     <row r="21">
@@ -1302,7 +1302,7 @@
         <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>15.90440478338968</v>
+        <v>15.90529663782263</v>
       </c>
     </row>
     <row r="22">
@@ -1343,7 +1343,7 @@
         <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>15.95062527901377</v>
+        <v>15.94907264007682</v>
       </c>
     </row>
     <row r="23">
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>16.47241871755802</v>
+        <v>16.46917095811485</v>
       </c>
     </row>
     <row r="24">
@@ -1425,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>16.47241871755802</v>
+        <v>16.46917095811485</v>
       </c>
     </row>
     <row r="25">
@@ -1466,7 +1466,7 @@
         <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>16.68125211750191</v>
+        <v>16.68150359318814</v>
       </c>
     </row>
     <row r="26">
@@ -1507,7 +1507,7 @@
         <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>17.13662195006867</v>
+        <v>17.13699864778113</v>
       </c>
     </row>
     <row r="27">
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>17.65643758803501</v>
+        <v>17.65606000717672</v>
       </c>
     </row>
     <row r="28">
@@ -1589,7 +1589,7 @@
         <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>17.726221843046</v>
+        <v>17.72686803633449</v>
       </c>
     </row>
     <row r="29">
@@ -1630,7 +1630,7 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>17.81936612530993</v>
+        <v>17.81944109171629</v>
       </c>
     </row>
     <row r="30">
@@ -1671,7 +1671,7 @@
         <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>17.83069852722052</v>
+        <v>17.82989940170764</v>
       </c>
     </row>
     <row r="31">
@@ -1712,7 +1712,7 @@
         <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>17.91045501285387</v>
+        <v>17.91105143658421</v>
       </c>
     </row>
     <row r="32">
@@ -1753,7 +1753,7 @@
         <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>18.11075800455528</v>
+        <v>18.11063187715624</v>
       </c>
     </row>
     <row r="33">
@@ -1794,7 +1794,7 @@
         <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>18.15983980085726</v>
+        <v>18.15987093947113</v>
       </c>
     </row>
     <row r="34">
@@ -1835,7 +1835,7 @@
         <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>18.15983980085726</v>
+        <v>18.15987093947113</v>
       </c>
     </row>
     <row r="35">
@@ -1876,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>18.25333437977661</v>
+        <v>18.25347872265014</v>
       </c>
     </row>
     <row r="36">
@@ -1917,7 +1917,7 @@
         <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>18.31313623191253</v>
+        <v>18.31300880162258</v>
       </c>
     </row>
     <row r="37">
@@ -1958,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>18.19251281614148</v>
+        <v>18.18374248726346</v>
       </c>
     </row>
     <row r="38">
@@ -1999,7 +1999,7 @@
         <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>18.32725138968634</v>
+        <v>18.32489867741947</v>
       </c>
     </row>
     <row r="39">
@@ -2040,7 +2040,7 @@
         <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>18.32725138968634</v>
+        <v>18.32489867741947</v>
       </c>
     </row>
     <row r="40">
@@ -2081,7 +2081,7 @@
         <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>18.43101520147438</v>
+        <v>18.43115021407112</v>
       </c>
     </row>
     <row r="41">
@@ -2122,7 +2122,7 @@
         <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>18.5685952563802</v>
+        <v>18.56838849707095</v>
       </c>
     </row>
     <row r="42">
@@ -2163,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>18.58008141167307</v>
+        <v>18.58191783635835</v>
       </c>
     </row>
     <row r="43">
@@ -2204,7 +2204,7 @@
         <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>18.83955821569582</v>
+        <v>18.84045488162381</v>
       </c>
     </row>
     <row r="44">
@@ -2245,7 +2245,7 @@
         <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>18.7683839298948</v>
+        <v>18.76887581351305</v>
       </c>
     </row>
     <row r="45">
@@ -2286,7 +2286,7 @@
         <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>18.73776743207468</v>
+        <v>18.74229667334115</v>
       </c>
     </row>
     <row r="46">
@@ -2327,7 +2327,7 @@
         <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>18.54743048859889</v>
+        <v>18.54653760366034</v>
       </c>
     </row>
     <row r="47">
@@ -2368,7 +2368,7 @@
         <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>18.15252804766378</v>
+        <v>18.15454817016082</v>
       </c>
     </row>
     <row r="48">
@@ -2409,7 +2409,7 @@
         <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>18.08003792003841</v>
+        <v>18.08007013293001</v>
       </c>
     </row>
     <row r="49">
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>18.0508829171354</v>
+        <v>18.04915627873921</v>
       </c>
     </row>
     <row r="50">
@@ -2491,7 +2491,7 @@
         <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>17.99032586218531</v>
+        <v>17.98837875632599</v>
       </c>
     </row>
     <row r="51">
@@ -2532,7 +2532,7 @@
         <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>17.99032586218531</v>
+        <v>17.98837875632599</v>
       </c>
     </row>
     <row r="52">
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>17.7490806393877</v>
+        <v>17.74861576103778</v>
       </c>
     </row>
     <row r="53">
@@ -2614,7 +2614,7 @@
         <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>17.74969718700408</v>
+        <v>17.74812266773921</v>
       </c>
     </row>
     <row r="54">
@@ -2655,7 +2655,7 @@
         <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>17.74969718700408</v>
+        <v>17.74812266773921</v>
       </c>
     </row>
     <row r="55">
@@ -2696,7 +2696,7 @@
         <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>17.81814662802715</v>
+        <v>17.79881074691802</v>
       </c>
     </row>
     <row r="56">
@@ -2737,7 +2737,7 @@
         <v>5</v>
       </c>
       <c r="K56" t="n">
-        <v>17.99225470919088</v>
+        <v>17.97859383075771</v>
       </c>
     </row>
     <row r="57">
@@ -2778,7 +2778,7 @@
         <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>18.04864477364506</v>
+        <v>18.04209307204975</v>
       </c>
     </row>
     <row r="58">
@@ -2819,7 +2819,7 @@
         <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>18.06393349092241</v>
+        <v>18.05583693465113</v>
       </c>
     </row>
     <row r="59">
@@ -2860,7 +2860,7 @@
         <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>18.25587384616591</v>
+        <v>18.25537619819129</v>
       </c>
     </row>
     <row r="60">
@@ -2901,7 +2901,7 @@
         <v>5</v>
       </c>
       <c r="K60" t="n">
-        <v>18.25587384616591</v>
+        <v>18.25537619819129</v>
       </c>
     </row>
     <row r="61">
@@ -2942,7 +2942,7 @@
         <v>5</v>
       </c>
       <c r="K61" t="n">
-        <v>18.26553935250956</v>
+        <v>18.26535630570529</v>
       </c>
     </row>
     <row r="62">
@@ -2983,7 +2983,7 @@
         <v>5</v>
       </c>
       <c r="K62" t="n">
-        <v>18.25615665036968</v>
+        <v>18.25543714052691</v>
       </c>
     </row>
     <row r="63">
@@ -3024,7 +3024,7 @@
         <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>18.32865305918012</v>
+        <v>18.35082486847733</v>
       </c>
     </row>
     <row r="64">
@@ -3065,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>18.22115293721825</v>
+        <v>18.31842442556919</v>
       </c>
     </row>
     <row r="65">
@@ -3106,7 +3106,7 @@
         <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>18.30135144683257</v>
+        <v>18.31842442556919</v>
       </c>
     </row>
     <row r="66">
@@ -3147,7 +3147,7 @@
         <v>5</v>
       </c>
       <c r="K66" t="n">
-        <v>18.33354581660341</v>
+        <v>18.3533122614999</v>
       </c>
     </row>
     <row r="67">
@@ -3188,7 +3188,7 @@
         <v>5</v>
       </c>
       <c r="K67" t="n">
-        <v>18.56867116826499</v>
+        <v>18.62276903281257</v>
       </c>
     </row>
     <row r="68">
@@ -3229,7 +3229,7 @@
         <v>5</v>
       </c>
       <c r="K68" t="n">
-        <v>19.21730918670944</v>
+        <v>19.36546901145579</v>
       </c>
     </row>
     <row r="69">
@@ -3270,7 +3270,7 @@
         <v>5</v>
       </c>
       <c r="K69" t="n">
-        <v>19.93538345298557</v>
+        <v>19.89377638396549</v>
       </c>
     </row>
     <row r="70">
@@ -3311,7 +3311,7 @@
         <v>5</v>
       </c>
       <c r="K70" t="n">
-        <v>19.93538345298557</v>
+        <v>19.89377638396549</v>
       </c>
     </row>
     <row r="71">
@@ -3352,7 +3352,7 @@
         <v>5</v>
       </c>
       <c r="K71" t="n">
-        <v>20.00981556112236</v>
+        <v>19.95730210915573</v>
       </c>
     </row>
     <row r="72">
@@ -3393,7 +3393,7 @@
         <v>5</v>
       </c>
       <c r="K72" t="n">
-        <v>20.00981556112236</v>
+        <v>19.95730210915573</v>
       </c>
     </row>
     <row r="73">
@@ -3434,7 +3434,7 @@
         <v>5</v>
       </c>
       <c r="K73" t="n">
-        <v>21.13985137760104</v>
+        <v>21.00429376107303</v>
       </c>
     </row>
     <row r="74">
@@ -3475,7 +3475,7 @@
         <v>5</v>
       </c>
       <c r="K74" t="n">
-        <v>21.25752534241971</v>
+        <v>21.19153026999809</v>
       </c>
     </row>
     <row r="75">
@@ -3516,7 +3516,7 @@
         <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>21.24478764721551</v>
+        <v>21.20271511536878</v>
       </c>
     </row>
     <row r="76">
@@ -3557,7 +3557,7 @@
         <v>6</v>
       </c>
       <c r="K76" t="n">
-        <v>21.24478764721551</v>
+        <v>21.20271511536878</v>
       </c>
     </row>
     <row r="77">
@@ -3598,7 +3598,7 @@
         <v>6</v>
       </c>
       <c r="K77" t="n">
-        <v>20.91401769073484</v>
+        <v>0.6098121915157551</v>
       </c>
     </row>
     <row r="78">
@@ -3639,7 +3639,7 @@
         <v>6</v>
       </c>
       <c r="K78" t="n">
-        <v>21.75249733392203</v>
+        <v>22.81637576394737</v>
       </c>
     </row>
     <row r="79">
@@ -3680,7 +3680,7 @@
         <v>6</v>
       </c>
       <c r="K79" t="n">
-        <v>18.31538578099143</v>
+        <v>22.45144185382393</v>
       </c>
     </row>
     <row r="80">
@@ -3721,7 +3721,7 @@
         <v>6</v>
       </c>
       <c r="K80" t="n">
-        <v>18.31538578099143</v>
+        <v>22.45144185382393</v>
       </c>
     </row>
     <row r="81">
@@ -3762,7 +3762,7 @@
         <v>6</v>
       </c>
       <c r="K81" t="n">
-        <v>41.15307330033042</v>
+        <v>0.8260418668445116</v>
       </c>
     </row>
     <row r="82">
@@ -3803,7 +3803,7 @@
         <v>6</v>
       </c>
       <c r="K82" t="n">
-        <v>55.6368087571851</v>
+        <v>56.23003942877807</v>
       </c>
     </row>
     <row r="83">
@@ -3844,7 +3844,7 @@
         <v>6</v>
       </c>
       <c r="K83" t="n">
-        <v>42.99916497611289</v>
+        <v>45.66360168374498</v>
       </c>
     </row>
     <row r="84">
@@ -3885,7 +3885,7 @@
         <v>6</v>
       </c>
       <c r="K84" t="n">
-        <v>40.56424938189363</v>
+        <v>40.59325963239543</v>
       </c>
     </row>
     <row r="85">
@@ -3926,7 +3926,7 @@
         <v>6</v>
       </c>
       <c r="K85" t="n">
-        <v>33.49840842426605</v>
+        <v>33.47802446979679</v>
       </c>
     </row>
     <row r="86">
@@ -3967,7 +3967,7 @@
         <v>6</v>
       </c>
       <c r="K86" t="n">
-        <v>23.51115280153341</v>
+        <v>23.49332569301106</v>
       </c>
     </row>
     <row r="87">
@@ -4008,7 +4008,7 @@
         <v>6</v>
       </c>
       <c r="K87" t="n">
-        <v>23.07759859367414</v>
+        <v>23.23111356074586</v>
       </c>
     </row>
     <row r="88">
@@ -4049,7 +4049,7 @@
         <v>6</v>
       </c>
       <c r="K88" t="n">
-        <v>23.03288491493475</v>
+        <v>23.01582633742614</v>
       </c>
     </row>
     <row r="89">
@@ -4090,7 +4090,7 @@
         <v>6</v>
       </c>
       <c r="K89" t="n">
-        <v>22.66480968815676</v>
+        <v>26.24216908963513</v>
       </c>
     </row>
     <row r="90">
@@ -4131,7 +4131,7 @@
         <v>6</v>
       </c>
       <c r="K90" t="n">
-        <v>22.62487457301624</v>
+        <v>24.43540424109552</v>
       </c>
     </row>
     <row r="91">
@@ -4172,7 +4172,7 @@
         <v>6</v>
       </c>
       <c r="K91" t="n">
-        <v>22.35957699356508</v>
+        <v>22.3884218643085</v>
       </c>
     </row>
     <row r="92">
@@ -4213,7 +4213,7 @@
         <v>6</v>
       </c>
       <c r="K92" t="n">
-        <v>22.35957699356508</v>
+        <v>22.3884218643085</v>
       </c>
     </row>
     <row r="93">
@@ -4254,7 +4254,7 @@
         <v>6</v>
       </c>
       <c r="K93" t="n">
-        <v>22.4810658565194</v>
+        <v>22.44510803430239</v>
       </c>
     </row>
     <row r="94">
@@ -4295,7 +4295,7 @@
         <v>6</v>
       </c>
       <c r="K94" t="n">
-        <v>23.00388300949592</v>
+        <v>22.49401812226683</v>
       </c>
     </row>
     <row r="95">
@@ -4336,7 +4336,7 @@
         <v>6</v>
       </c>
       <c r="K95" t="n">
-        <v>22.60724382801739</v>
+        <v>22.49694087128349</v>
       </c>
     </row>
     <row r="96">
@@ -4377,7 +4377,7 @@
         <v>6</v>
       </c>
       <c r="K96" t="n">
-        <v>22.41499665150971</v>
+        <v>22.19039193738289</v>
       </c>
     </row>
     <row r="97">
@@ -4418,7 +4418,7 @@
         <v>6</v>
       </c>
       <c r="K97" t="n">
-        <v>21.77700237518826</v>
+        <v>21.76284238497333</v>
       </c>
     </row>
     <row r="98">
@@ -4459,7 +4459,7 @@
         <v>6</v>
       </c>
       <c r="K98" t="n">
-        <v>21.77700237518826</v>
+        <v>21.76284238497333</v>
       </c>
     </row>
     <row r="99">
@@ -4500,7 +4500,7 @@
         <v>6</v>
       </c>
       <c r="K99" t="n">
-        <v>25.95407996901959</v>
+        <v>21.65492269454226</v>
       </c>
     </row>
     <row r="100">
@@ -4541,7 +4541,7 @@
         <v>6</v>
       </c>
       <c r="K100" t="n">
-        <v>20.6651522369616</v>
+        <v>20.57281945073719</v>
       </c>
     </row>
     <row r="101">
@@ -4582,7 +4582,7 @@
         <v>6</v>
       </c>
       <c r="K101" t="n">
-        <v>20.58203948620306</v>
+        <v>20.50179656936968</v>
       </c>
     </row>
     <row r="102">
@@ -4623,7 +4623,7 @@
         <v>6</v>
       </c>
       <c r="K102" t="n">
-        <v>20.05324427496122</v>
+        <v>20.1367742844572</v>
       </c>
     </row>
     <row r="103">
@@ -4664,7 +4664,7 @@
         <v>6</v>
       </c>
       <c r="K103" t="n">
-        <v>20.05324427496122</v>
+        <v>20.1367742844572</v>
       </c>
     </row>
     <row r="104">
@@ -4705,7 +4705,7 @@
         <v>6</v>
       </c>
       <c r="K104" t="n">
-        <v>10.13286816744238</v>
+        <v>10.05556289128236</v>
       </c>
     </row>
     <row r="105">
@@ -4746,7 +4746,7 @@
         <v>6</v>
       </c>
       <c r="K105" t="n">
-        <v>10.13286816744238</v>
+        <v>10.05556289128236</v>
       </c>
     </row>
     <row r="106">
@@ -4787,7 +4787,7 @@
         <v>6</v>
       </c>
       <c r="K106" t="n">
-        <v>9.313454523502497</v>
+        <v>9.249788548710319</v>
       </c>
     </row>
     <row r="107">
@@ -4828,7 +4828,7 @@
         <v>6</v>
       </c>
       <c r="K107" t="n">
-        <v>9.313454523502497</v>
+        <v>9.249788548710319</v>
       </c>
     </row>
     <row r="108">
@@ -4869,7 +4869,7 @@
         <v>6</v>
       </c>
       <c r="K108" t="n">
-        <v>9.006605764587595</v>
+        <v>9.001199936508684</v>
       </c>
     </row>
     <row r="109">
@@ -4910,7 +4910,7 @@
         <v>6</v>
       </c>
       <c r="K109" t="n">
-        <v>8.855391791179059</v>
+        <v>8.859202453554882</v>
       </c>
     </row>
     <row r="110">
@@ -4951,7 +4951,7 @@
         <v>6</v>
       </c>
       <c r="K110" t="n">
-        <v>8.978645588225934</v>
+        <v>8.984742925862029</v>
       </c>
     </row>
     <row r="111">
@@ -4992,7 +4992,7 @@
         <v>6</v>
       </c>
       <c r="K111" t="n">
-        <v>8.984199379338564</v>
+        <v>8.988563827679902</v>
       </c>
     </row>
     <row r="112">
@@ -5033,7 +5033,7 @@
         <v>6</v>
       </c>
       <c r="K112" t="n">
-        <v>9.061980501635373</v>
+        <v>9.057072937995757</v>
       </c>
     </row>
     <row r="113">
@@ -5074,7 +5074,7 @@
         <v>6</v>
       </c>
       <c r="K113" t="n">
-        <v>9.061980501635373</v>
+        <v>9.057072937995757</v>
       </c>
     </row>
     <row r="114">
@@ -5115,7 +5115,7 @@
         <v>6</v>
       </c>
       <c r="K114" t="n">
-        <v>9.044872040221554</v>
+        <v>9.045523308623421</v>
       </c>
     </row>
     <row r="115">
@@ -5156,7 +5156,7 @@
         <v>6</v>
       </c>
       <c r="K115" t="n">
-        <v>8.817828618037916</v>
+        <v>8.809891251011997</v>
       </c>
     </row>
     <row r="116">
@@ -5197,7 +5197,7 @@
         <v>6</v>
       </c>
       <c r="K116" t="n">
-        <v>8.013828136438326</v>
+        <v>8.01349959414503</v>
       </c>
     </row>
     <row r="117">
@@ -5238,7 +5238,7 @@
         <v>6</v>
       </c>
       <c r="K117" t="n">
-        <v>7.881424971903225</v>
+        <v>7.879726061462629</v>
       </c>
     </row>
     <row r="118">
@@ -5279,7 +5279,7 @@
         <v>6</v>
       </c>
       <c r="K118" t="n">
-        <v>7.614794171987974</v>
+        <v>7.613353376700388</v>
       </c>
     </row>
     <row r="119">
@@ -5320,7 +5320,7 @@
         <v>6</v>
       </c>
       <c r="K119" t="n">
-        <v>7.614794171987974</v>
+        <v>7.613353376700388</v>
       </c>
     </row>
     <row r="120">
@@ -5361,7 +5361,7 @@
         <v>6</v>
       </c>
       <c r="K120" t="n">
-        <v>7.525888632454506</v>
+        <v>7.52583147660655</v>
       </c>
     </row>
     <row r="121">
@@ -5402,7 +5402,7 @@
         <v>6</v>
       </c>
       <c r="K121" t="n">
-        <v>7.648109426969325</v>
+        <v>7.649937527108574</v>
       </c>
     </row>
     <row r="122">
@@ -5443,7 +5443,7 @@
         <v>6</v>
       </c>
       <c r="K122" t="n">
-        <v>7.833439394377753</v>
+        <v>7.834451497123795</v>
       </c>
     </row>
     <row r="123">
@@ -5484,7 +5484,7 @@
         <v>6</v>
       </c>
       <c r="K123" t="n">
-        <v>7.877726027147521</v>
+        <v>7.878513743038085</v>
       </c>
     </row>
     <row r="124">
@@ -5525,7 +5525,7 @@
         <v>6</v>
       </c>
       <c r="K124" t="n">
-        <v>7.996504394876585</v>
+        <v>7.996384831667157</v>
       </c>
     </row>
     <row r="125">
@@ -5566,7 +5566,7 @@
         <v>6</v>
       </c>
       <c r="K125" t="n">
-        <v>8.026213232574577</v>
+        <v>8.026924327986121</v>
       </c>
     </row>
     <row r="126">
@@ -5607,7 +5607,7 @@
         <v>6</v>
       </c>
       <c r="K126" t="n">
-        <v>8.026213232574577</v>
+        <v>8.026924327986121</v>
       </c>
     </row>
     <row r="127">
@@ -5648,7 +5648,7 @@
         <v>6</v>
       </c>
       <c r="K127" t="n">
-        <v>8.218318514120106</v>
+        <v>8.215642482556708</v>
       </c>
     </row>
     <row r="128">
@@ -5689,7 +5689,7 @@
         <v>6</v>
       </c>
       <c r="K128" t="n">
-        <v>8.233471211243319</v>
+        <v>8.234901432720093</v>
       </c>
     </row>
     <row r="129">
@@ -5730,7 +5730,7 @@
         <v>6</v>
       </c>
       <c r="K129" t="n">
-        <v>8.33695754632191</v>
+        <v>8.338770570052079</v>
       </c>
     </row>
     <row r="130">
@@ -5771,7 +5771,7 @@
         <v>6</v>
       </c>
       <c r="K130" t="n">
-        <v>8.659828082032606</v>
+        <v>8.661114516403142</v>
       </c>
     </row>
     <row r="131">
@@ -5812,7 +5812,7 @@
         <v>6</v>
       </c>
       <c r="K131" t="n">
-        <v>8.955520418282028</v>
+        <v>8.957982002673143</v>
       </c>
     </row>
     <row r="132">
@@ -5853,7 +5853,7 @@
         <v>6</v>
       </c>
       <c r="K132" t="n">
-        <v>9.117370986390577</v>
+        <v>9.118840462178738</v>
       </c>
     </row>
     <row r="133">
@@ -5894,7 +5894,7 @@
         <v>6</v>
       </c>
       <c r="K133" t="n">
-        <v>9.182150333628899</v>
+        <v>9.184142659321292</v>
       </c>
     </row>
     <row r="134">
@@ -5935,7 +5935,7 @@
         <v>6</v>
       </c>
       <c r="K134" t="n">
-        <v>9.502707810945383</v>
+        <v>9.503947719470569</v>
       </c>
     </row>
     <row r="135">
@@ -5976,7 +5976,7 @@
         <v>6</v>
       </c>
       <c r="K135" t="n">
-        <v>9.58700817278682</v>
+        <v>9.601021663415642</v>
       </c>
     </row>
     <row r="136">
@@ -6017,7 +6017,7 @@
         <v>6</v>
       </c>
       <c r="K136" t="n">
-        <v>9.600055061876473</v>
+        <v>9.601021663415642</v>
       </c>
     </row>
     <row r="137">
@@ -6058,7 +6058,7 @@
         <v>6</v>
       </c>
       <c r="K137" t="n">
-        <v>9.666185798546529</v>
+        <v>9.667080517255647</v>
       </c>
     </row>
     <row r="138">
@@ -6099,7 +6099,7 @@
         <v>6</v>
       </c>
       <c r="K138" t="n">
-        <v>9.747179920199084</v>
+        <v>9.748095555311115</v>
       </c>
     </row>
     <row r="139">
@@ -6140,7 +6140,7 @@
         <v>6</v>
       </c>
       <c r="K139" t="n">
-        <v>9.919536055839442</v>
+        <v>9.920481651612979</v>
       </c>
     </row>
     <row r="140">
@@ -6181,7 +6181,7 @@
         <v>6</v>
       </c>
       <c r="K140" t="n">
-        <v>10.03982707763049</v>
+        <v>10.03384085376461</v>
       </c>
     </row>
     <row r="141">
@@ -6222,7 +6222,7 @@
         <v>6</v>
       </c>
       <c r="K141" t="n">
-        <v>10.10075936227274</v>
+        <v>10.04873175068141</v>
       </c>
     </row>
     <row r="142">
@@ -6263,7 +6263,7 @@
         <v>6</v>
       </c>
       <c r="K142" t="n">
-        <v>10.18523871563691</v>
+        <v>10.1703113821572</v>
       </c>
     </row>
     <row r="143">
@@ -6304,7 +6304,7 @@
         <v>6</v>
       </c>
       <c r="K143" t="n">
-        <v>10.18523871563691</v>
+        <v>10.1703113821572</v>
       </c>
     </row>
     <row r="144">
@@ -6345,7 +6345,7 @@
         <v>6</v>
       </c>
       <c r="K144" t="n">
-        <v>10.3241301980949</v>
+        <v>10.32652469704417</v>
       </c>
     </row>
     <row r="145">
@@ -6386,7 +6386,7 @@
         <v>6</v>
       </c>
       <c r="K145" t="n">
-        <v>10.3241301980949</v>
+        <v>10.32652469704417</v>
       </c>
     </row>
     <row r="146">
@@ -6427,7 +6427,7 @@
         <v>6</v>
       </c>
       <c r="K146" t="n">
-        <v>10.72804752206529</v>
+        <v>10.73329757505697</v>
       </c>
     </row>
     <row r="147">
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="K147" t="n">
-        <v>10.82821853712411</v>
+        <v>10.83205391069262</v>
       </c>
     </row>
     <row r="148">
@@ -6509,7 +6509,7 @@
         <v>6</v>
       </c>
       <c r="K148" t="n">
-        <v>11.31153344108232</v>
+        <v>11.34493953621662</v>
       </c>
     </row>
     <row r="149">
@@ -6550,7 +6550,7 @@
         <v>6</v>
       </c>
       <c r="K149" t="n">
-        <v>11.3428515747395</v>
+        <v>11.34493953621662</v>
       </c>
     </row>
     <row r="150">
@@ -6591,7 +6591,7 @@
         <v>6</v>
       </c>
       <c r="K150" t="n">
-        <v>11.56598692004501</v>
+        <v>11.56684451772449</v>
       </c>
     </row>
     <row r="151">
@@ -6632,7 +6632,7 @@
         <v>6</v>
       </c>
       <c r="K151" t="n">
-        <v>11.58221626307304</v>
+        <v>11.58198326305179</v>
       </c>
     </row>
     <row r="152">
@@ -6673,7 +6673,7 @@
         <v>6</v>
       </c>
       <c r="K152" t="n">
-        <v>11.6068897425725</v>
+        <v>11.60728634568303</v>
       </c>
     </row>
     <row r="153">
@@ -6714,7 +6714,7 @@
         <v>6</v>
       </c>
       <c r="K153" t="n">
-        <v>11.6490487157816</v>
+        <v>11.65030216584749</v>
       </c>
     </row>
     <row r="154">
@@ -6755,7 +6755,7 @@
         <v>6</v>
       </c>
       <c r="K154" t="n">
-        <v>12.28759492419801</v>
+        <v>12.28927385385947</v>
       </c>
     </row>
     <row r="155">
@@ -6796,7 +6796,7 @@
         <v>6</v>
       </c>
       <c r="K155" t="n">
-        <v>12.54621779554327</v>
+        <v>12.54816392343241</v>
       </c>
     </row>
     <row r="156">
@@ -6837,7 +6837,7 @@
         <v>6</v>
       </c>
       <c r="K156" t="n">
-        <v>12.57078394962207</v>
+        <v>12.56367312450933</v>
       </c>
     </row>
     <row r="157">
@@ -6878,7 +6878,7 @@
         <v>6</v>
       </c>
       <c r="K157" t="n">
-        <v>12.73187879407693</v>
+        <v>12.73286697894567</v>
       </c>
     </row>
     <row r="158">
@@ -6919,7 +6919,7 @@
         <v>6</v>
       </c>
       <c r="K158" t="n">
-        <v>12.90081744954813</v>
+        <v>12.90108600673018</v>
       </c>
     </row>
     <row r="159">
@@ -6960,7 +6960,7 @@
         <v>6</v>
       </c>
       <c r="K159" t="n">
-        <v>12.73729214372356</v>
+        <v>12.73686903582316</v>
       </c>
     </row>
     <row r="160">
@@ -7001,7 +7001,7 @@
         <v>6</v>
       </c>
       <c r="K160" t="n">
-        <v>12.61379930677621</v>
+        <v>12.61285613536885</v>
       </c>
     </row>
     <row r="161">
@@ -7042,7 +7042,7 @@
         <v>6</v>
       </c>
       <c r="K161" t="n">
-        <v>12.48481118538775</v>
+        <v>12.48423020315763</v>
       </c>
     </row>
     <row r="162">
@@ -7083,7 +7083,7 @@
         <v>6</v>
       </c>
       <c r="K162" t="n">
-        <v>12.17667309377143</v>
+        <v>12.17615535638471</v>
       </c>
     </row>
     <row r="163">
@@ -7124,7 +7124,7 @@
         <v>6</v>
       </c>
       <c r="K163" t="n">
-        <v>12.09432674237669</v>
+        <v>12.0939672988404</v>
       </c>
     </row>
     <row r="164">
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="K164" t="n">
-        <v>12.31599521887282</v>
+        <v>12.30220165692974</v>
       </c>
     </row>
     <row r="165">
@@ -7206,7 +7206,7 @@
         <v>6</v>
       </c>
       <c r="K165" t="n">
-        <v>12.5062115616939</v>
+        <v>12.50813670960662</v>
       </c>
     </row>
     <row r="166">
@@ -7247,7 +7247,7 @@
         <v>6</v>
       </c>
       <c r="K166" t="n">
-        <v>13.12036788826173</v>
+        <v>13.12139488965561</v>
       </c>
     </row>
     <row r="167">
@@ -7288,7 +7288,7 @@
         <v>6</v>
       </c>
       <c r="K167" t="n">
-        <v>13.1463425367316</v>
+        <v>13.1377199395177</v>
       </c>
     </row>
     <row r="168">
@@ -7329,7 +7329,7 @@
         <v>6</v>
       </c>
       <c r="K168" t="n">
-        <v>13.18008131564125</v>
+        <v>13.18039755108718</v>
       </c>
     </row>
     <row r="169">
@@ -7370,7 +7370,7 @@
         <v>6</v>
       </c>
       <c r="K169" t="n">
-        <v>13.40114512882637</v>
+        <v>13.40216427255851</v>
       </c>
     </row>
     <row r="170">
@@ -7411,7 +7411,7 @@
         <v>6</v>
       </c>
       <c r="K170" t="n">
-        <v>13.51724608384559</v>
+        <v>13.51770449706086</v>
       </c>
     </row>
     <row r="171">
@@ -7452,7 +7452,7 @@
         <v>6</v>
       </c>
       <c r="K171" t="n">
-        <v>13.51724608384559</v>
+        <v>13.51770449706086</v>
       </c>
     </row>
     <row r="172">
@@ -7493,7 +7493,7 @@
         <v>6</v>
       </c>
       <c r="K172" t="n">
-        <v>13.45049177307704</v>
+        <v>13.42834726587935</v>
       </c>
     </row>
     <row r="173">
@@ -7534,7 +7534,7 @@
         <v>6</v>
       </c>
       <c r="K173" t="n">
-        <v>13.41663382802796</v>
+        <v>13.42834726587935</v>
       </c>
     </row>
     <row r="174">
@@ -7575,7 +7575,7 @@
         <v>6</v>
       </c>
       <c r="K174" t="n">
-        <v>13.1360587715864</v>
+        <v>13.13596054003147</v>
       </c>
     </row>
     <row r="175">
@@ -7616,7 +7616,7 @@
         <v>6</v>
       </c>
       <c r="K175" t="n">
-        <v>12.383252203665</v>
+        <v>12.3818195935645</v>
       </c>
     </row>
     <row r="176">
@@ -7657,7 +7657,7 @@
         <v>6</v>
       </c>
       <c r="K176" t="n">
-        <v>12.32503009871696</v>
+        <v>12.34488939642437</v>
       </c>
     </row>
     <row r="177">
@@ -7698,7 +7698,7 @@
         <v>6</v>
       </c>
       <c r="K177" t="n">
-        <v>11.8644104980694</v>
+        <v>11.86363453966294</v>
       </c>
     </row>
     <row r="178">
@@ -7739,7 +7739,7 @@
         <v>6</v>
       </c>
       <c r="K178" t="n">
-        <v>11.66991607980337</v>
+        <v>11.66917292052748</v>
       </c>
     </row>
     <row r="179">
@@ -7780,7 +7780,7 @@
         <v>6</v>
       </c>
       <c r="K179" t="n">
-        <v>11.4397626168475</v>
+        <v>11.44003729032269</v>
       </c>
     </row>
     <row r="180">
@@ -7821,7 +7821,7 @@
         <v>6</v>
       </c>
       <c r="K180" t="n">
-        <v>11.37121225770263</v>
+        <v>11.37095695966775</v>
       </c>
     </row>
     <row r="181">
@@ -7862,7 +7862,7 @@
         <v>6</v>
       </c>
       <c r="K181" t="n">
-        <v>11.08346970895239</v>
+        <v>11.0824964530113</v>
       </c>
     </row>
     <row r="182">
@@ -7903,7 +7903,7 @@
         <v>6</v>
       </c>
       <c r="K182" t="n">
-        <v>11.09012132545501</v>
+        <v>11.09009195586846</v>
       </c>
     </row>
     <row r="183">
@@ -7944,7 +7944,7 @@
         <v>6</v>
       </c>
       <c r="K183" t="n">
-        <v>11.1133397312677</v>
+        <v>11.11346172376633</v>
       </c>
     </row>
     <row r="184">
@@ -7985,7 +7985,7 @@
         <v>6</v>
       </c>
       <c r="K184" t="n">
-        <v>11.38285727695747</v>
+        <v>11.38295853545234</v>
       </c>
     </row>
     <row r="185">
@@ -8026,7 +8026,7 @@
         <v>6</v>
       </c>
       <c r="K185" t="n">
-        <v>11.40930901230741</v>
+        <v>11.40906398075885</v>
       </c>
     </row>
     <row r="186">
@@ -8067,7 +8067,7 @@
         <v>7</v>
       </c>
       <c r="K186" t="n">
-        <v>11.63847912745985</v>
+        <v>11.63801176927609</v>
       </c>
     </row>
     <row r="187">
@@ -8108,7 +8108,7 @@
         <v>7</v>
       </c>
       <c r="K187" t="n">
-        <v>12.23669714585852</v>
+        <v>12.23561229550869</v>
       </c>
     </row>
     <row r="188">
@@ -8149,7 +8149,7 @@
         <v>7</v>
       </c>
       <c r="K188" t="n">
-        <v>12.32498885385217</v>
+        <v>12.32493800141896</v>
       </c>
     </row>
     <row r="189">
@@ -8190,7 +8190,7 @@
         <v>7</v>
       </c>
       <c r="K189" t="n">
-        <v>12.6846002976039</v>
+        <v>12.68439321587084</v>
       </c>
     </row>
     <row r="190">
@@ -8231,7 +8231,7 @@
         <v>7</v>
       </c>
       <c r="K190" t="n">
-        <v>13.02992558520946</v>
+        <v>13.02958147828541</v>
       </c>
     </row>
     <row r="191">
@@ -8272,7 +8272,7 @@
         <v>7</v>
       </c>
       <c r="K191" t="n">
-        <v>13.11080079318839</v>
+        <v>13.10942074896131</v>
       </c>
     </row>
     <row r="192">
@@ -8313,7 +8313,7 @@
         <v>7</v>
       </c>
       <c r="K192" t="n">
-        <v>13.23499422520247</v>
+        <v>13.21905420441579</v>
       </c>
     </row>
     <row r="193">
@@ -8354,7 +8354,7 @@
         <v>7</v>
       </c>
       <c r="K193" t="n">
-        <v>13.38869754162123</v>
+        <v>13.41609389853743</v>
       </c>
     </row>
     <row r="194">
@@ -8395,7 +8395,7 @@
         <v>7</v>
       </c>
       <c r="K194" t="n">
-        <v>13.84081620532295</v>
+        <v>13.85685042720981</v>
       </c>
     </row>
     <row r="195">
@@ -8436,7 +8436,7 @@
         <v>7</v>
       </c>
       <c r="K195" t="n">
-        <v>13.85513475154574</v>
+        <v>13.85685042720981</v>
       </c>
     </row>
     <row r="196">
@@ -8477,7 +8477,7 @@
         <v>7</v>
       </c>
       <c r="K196" t="n">
-        <v>13.85513475154574</v>
+        <v>13.85685042720981</v>
       </c>
     </row>
     <row r="197">
@@ -8518,7 +8518,7 @@
         <v>7</v>
       </c>
       <c r="K197" t="n">
-        <v>13.89603621482746</v>
+        <v>13.90173162460115</v>
       </c>
     </row>
     <row r="198">
@@ -8559,7 +8559,7 @@
         <v>7</v>
       </c>
       <c r="K198" t="n">
-        <v>13.08301745600236</v>
+        <v>13.08958004473499</v>
       </c>
     </row>
     <row r="199">
@@ -8600,7 +8600,7 @@
         <v>7</v>
       </c>
       <c r="K199" t="n">
-        <v>13.08301745600236</v>
+        <v>13.08958004473499</v>
       </c>
     </row>
     <row r="200">
@@ -8641,7 +8641,7 @@
         <v>7</v>
       </c>
       <c r="K200" t="n">
-        <v>12.79344106631639</v>
+        <v>12.78976864218879</v>
       </c>
     </row>
     <row r="201">
@@ -8682,7 +8682,7 @@
         <v>7</v>
       </c>
       <c r="K201" t="n">
-        <v>12.79344106631639</v>
+        <v>12.78976864218879</v>
       </c>
     </row>
     <row r="202">
@@ -8723,7 +8723,7 @@
         <v>7</v>
       </c>
       <c r="K202" t="n">
-        <v>12.00715379503883</v>
+        <v>12.02344956757194</v>
       </c>
     </row>
     <row r="203">
@@ -8764,7 +8764,7 @@
         <v>7</v>
       </c>
       <c r="K203" t="n">
-        <v>11.12071911562041</v>
+        <v>11.35486375876084</v>
       </c>
     </row>
     <row r="204">
@@ -8805,7 +8805,7 @@
         <v>7</v>
       </c>
       <c r="K204" t="n">
-        <v>10.85358927129134</v>
+        <v>10.84914955146178</v>
       </c>
     </row>
     <row r="205">
@@ -8846,7 +8846,7 @@
         <v>7</v>
       </c>
       <c r="K205" t="n">
-        <v>9.459045729439039</v>
+        <v>9.465079945180731</v>
       </c>
     </row>
     <row r="206">
@@ -8887,7 +8887,7 @@
         <v>7</v>
       </c>
       <c r="K206" t="n">
-        <v>9.437147962636711</v>
+        <v>9.429051361664438</v>
       </c>
     </row>
     <row r="207">
@@ -8928,7 +8928,7 @@
         <v>7</v>
       </c>
       <c r="K207" t="n">
-        <v>9.54143291222257</v>
+        <v>9.541355830426482</v>
       </c>
     </row>
     <row r="208">
@@ -8969,7 +8969,7 @@
         <v>7</v>
       </c>
       <c r="K208" t="n">
-        <v>9.625850753583549</v>
+        <v>9.630205530409832</v>
       </c>
     </row>
     <row r="209">
@@ -9010,7 +9010,7 @@
         <v>7</v>
       </c>
       <c r="K209" t="n">
-        <v>9.625850753583549</v>
+        <v>9.630205530409832</v>
       </c>
     </row>
     <row r="210">
@@ -9051,7 +9051,7 @@
         <v>7</v>
       </c>
       <c r="K210" t="n">
-        <v>12.38066397757235</v>
+        <v>12.33771936542497</v>
       </c>
     </row>
     <row r="211">
@@ -9092,7 +9092,7 @@
         <v>7</v>
       </c>
       <c r="K211" t="n">
-        <v>12.71821880589731</v>
+        <v>12.68143979333274</v>
       </c>
     </row>
     <row r="212">
@@ -9133,7 +9133,7 @@
         <v>7</v>
       </c>
       <c r="K212" t="n">
-        <v>13.44948705679101</v>
+        <v>13.44446385614669</v>
       </c>
     </row>
     <row r="213">
@@ -9174,7 +9174,7 @@
         <v>7</v>
       </c>
       <c r="K213" t="n">
-        <v>14.21732025284459</v>
+        <v>14.02459428668939</v>
       </c>
     </row>
     <row r="214">
@@ -9215,7 +9215,7 @@
         <v>7</v>
       </c>
       <c r="K214" t="n">
-        <v>14.21745677623078</v>
+        <v>14.21336218412485</v>
       </c>
     </row>
     <row r="215">
@@ -9256,7 +9256,7 @@
         <v>7</v>
       </c>
       <c r="K215" t="n">
-        <v>14.21745677623078</v>
+        <v>14.21336218412485</v>
       </c>
     </row>
     <row r="216">
@@ -9297,7 +9297,7 @@
         <v>7</v>
       </c>
       <c r="K216" t="n">
-        <v>14.25510820694356</v>
+        <v>14.23760632627079</v>
       </c>
     </row>
     <row r="217">
@@ -9338,7 +9338,7 @@
         <v>7</v>
       </c>
       <c r="K217" t="n">
-        <v>14.48563426810835</v>
+        <v>14.48428152654683</v>
       </c>
     </row>
     <row r="218">
@@ -9379,7 +9379,7 @@
         <v>7</v>
       </c>
       <c r="K218" t="n">
-        <v>14.41465342011496</v>
+        <v>14.41676964340713</v>
       </c>
     </row>
     <row r="219">
@@ -9420,7 +9420,7 @@
         <v>7</v>
       </c>
       <c r="K219" t="n">
-        <v>14.41465342011496</v>
+        <v>14.41676964340713</v>
       </c>
     </row>
     <row r="220">
@@ -9461,7 +9461,7 @@
         <v>7</v>
       </c>
       <c r="K220" t="n">
-        <v>14.39499340107542</v>
+        <v>14.4039811208747</v>
       </c>
     </row>
     <row r="221">
@@ -9502,7 +9502,7 @@
         <v>7</v>
       </c>
       <c r="K221" t="n">
-        <v>14.408006382966</v>
+        <v>14.39115198493066</v>
       </c>
     </row>
     <row r="222">
@@ -9543,7 +9543,7 @@
         <v>7</v>
       </c>
       <c r="K222" t="n">
-        <v>14.54077189549916</v>
+        <v>15.68537209978566</v>
       </c>
     </row>
     <row r="223">
@@ -9584,7 +9584,7 @@
         <v>7</v>
       </c>
       <c r="K223" t="n">
-        <v>14.56706940849767</v>
+        <v>14.55141868468563</v>
       </c>
     </row>
     <row r="224">
@@ -9625,7 +9625,7 @@
         <v>7</v>
       </c>
       <c r="K224" t="n">
-        <v>14.41123879058222</v>
+        <v>14.63775965186692</v>
       </c>
     </row>
     <row r="225">
@@ -9666,7 +9666,7 @@
         <v>7</v>
       </c>
       <c r="K225" t="n">
-        <v>9.734247449587954</v>
+        <v>9.742891111081873</v>
       </c>
     </row>
     <row r="226">
@@ -9707,7 +9707,7 @@
         <v>7</v>
       </c>
       <c r="K226" t="n">
-        <v>9.734247449587954</v>
+        <v>9.742891111081873</v>
       </c>
     </row>
     <row r="227">
@@ -9748,7 +9748,7 @@
         <v>7</v>
       </c>
       <c r="K227" t="n">
-        <v>9.593812835277401</v>
+        <v>9.598140150086556</v>
       </c>
     </row>
     <row r="228">
@@ -9789,7 +9789,7 @@
         <v>7</v>
       </c>
       <c r="K228" t="n">
-        <v>9.563180560247915</v>
+        <v>9.577943442830595</v>
       </c>
     </row>
     <row r="229">
@@ -9830,7 +9830,7 @@
         <v>7</v>
       </c>
       <c r="K229" t="n">
-        <v>9.32658839506702</v>
+        <v>9.328574182929387</v>
       </c>
     </row>
     <row r="230">
@@ -9871,7 +9871,7 @@
         <v>7</v>
       </c>
       <c r="K230" t="n">
-        <v>9.32658839506702</v>
+        <v>9.328574182929387</v>
       </c>
     </row>
     <row r="231">
@@ -9912,7 +9912,7 @@
         <v>7</v>
       </c>
       <c r="K231" t="n">
-        <v>9.212777979173321</v>
+        <v>9.215841458343096</v>
       </c>
     </row>
     <row r="232">
@@ -9953,7 +9953,7 @@
         <v>7</v>
       </c>
       <c r="K232" t="n">
-        <v>9.048349594171293</v>
+        <v>9.065450967498593</v>
       </c>
     </row>
     <row r="233">
@@ -9994,7 +9994,7 @@
         <v>7</v>
       </c>
       <c r="K233" t="n">
-        <v>9.048349594171293</v>
+        <v>8.944815767177214</v>
       </c>
     </row>
     <row r="234">
@@ -10035,7 +10035,7 @@
         <v>7</v>
       </c>
       <c r="K234" t="n">
-        <v>8.562581998394522</v>
+        <v>8.565077810158083</v>
       </c>
     </row>
     <row r="235">
@@ -10076,7 +10076,7 @@
         <v>7</v>
       </c>
       <c r="K235" t="n">
-        <v>8.54224868104124</v>
+        <v>8.550860831439831</v>
       </c>
     </row>
     <row r="236">
@@ -10117,7 +10117,7 @@
         <v>7</v>
       </c>
       <c r="K236" t="n">
-        <v>8.530053473915986</v>
+        <v>8.529971523309928</v>
       </c>
     </row>
     <row r="237">
@@ -10158,7 +10158,7 @@
         <v>7</v>
       </c>
       <c r="K237" t="n">
-        <v>8.536025446984272</v>
+        <v>8.534832785725014</v>
       </c>
     </row>
     <row r="238">
@@ -10199,7 +10199,7 @@
         <v>7</v>
       </c>
       <c r="K238" t="n">
-        <v>8.559446620806037</v>
+        <v>8.549542365725689</v>
       </c>
     </row>
     <row r="239">
@@ -10240,7 +10240,7 @@
         <v>7</v>
       </c>
       <c r="K239" t="n">
-        <v>8.586175230134678</v>
+        <v>8.577751456745935</v>
       </c>
     </row>
     <row r="240">
@@ -10281,7 +10281,7 @@
         <v>7</v>
       </c>
       <c r="K240" t="n">
-        <v>8.737150150974397</v>
+        <v>8.735219450043544</v>
       </c>
     </row>
     <row r="241">
@@ -10322,7 +10322,7 @@
         <v>7</v>
       </c>
       <c r="K241" t="n">
-        <v>8.76378572010505</v>
+        <v>8.748361677410891</v>
       </c>
     </row>
     <row r="242">
@@ -10363,7 +10363,7 @@
         <v>7</v>
       </c>
       <c r="K242" t="n">
-        <v>8.76378572010505</v>
+        <v>8.748361677410891</v>
       </c>
     </row>
     <row r="243">
@@ -10404,7 +10404,7 @@
         <v>7</v>
       </c>
       <c r="K243" t="n">
-        <v>8.76378572010505</v>
+        <v>8.810267990394754</v>
       </c>
     </row>
     <row r="244">
@@ -10445,7 +10445,7 @@
         <v>7</v>
       </c>
       <c r="K244" t="n">
-        <v>8.860497001708882</v>
+        <v>8.841626865901995</v>
       </c>
     </row>
     <row r="245">
@@ -10486,7 +10486,7 @@
         <v>7</v>
       </c>
       <c r="K245" t="n">
-        <v>8.728049327441687</v>
+        <v>8.706355136818491</v>
       </c>
     </row>
     <row r="246">
@@ -10527,7 +10527,7 @@
         <v>7</v>
       </c>
       <c r="K246" t="n">
-        <v>8.265998682229123</v>
+        <v>8.269488333551342</v>
       </c>
     </row>
     <row r="247">
@@ -10568,7 +10568,7 @@
         <v>7</v>
       </c>
       <c r="K247" t="n">
-        <v>8.023206549470904</v>
+        <v>8.045862914088417</v>
       </c>
     </row>
     <row r="248">
@@ -10609,7 +10609,7 @@
         <v>7</v>
       </c>
       <c r="K248" t="n">
-        <v>7.682841429451753</v>
+        <v>7.70126369523794</v>
       </c>
     </row>
     <row r="249">
@@ -10650,7 +10650,7 @@
         <v>7</v>
       </c>
       <c r="K249" t="n">
-        <v>7.426705554602476</v>
+        <v>7.429158110036173</v>
       </c>
     </row>
     <row r="250">
@@ -10691,7 +10691,7 @@
         <v>7</v>
       </c>
       <c r="K250" t="n">
-        <v>7.390699076518517</v>
+        <v>7.406152218319828</v>
       </c>
     </row>
     <row r="251">
@@ -10732,7 +10732,7 @@
         <v>7</v>
       </c>
       <c r="K251" t="n">
-        <v>7.27884898883527</v>
+        <v>7.291847534290575</v>
       </c>
     </row>
     <row r="252">
@@ -10773,7 +10773,7 @@
         <v>7</v>
       </c>
       <c r="K252" t="n">
-        <v>7.073104492826911</v>
+        <v>7.085970062187926</v>
       </c>
     </row>
     <row r="253">
@@ -10814,7 +10814,7 @@
         <v>7</v>
       </c>
       <c r="K253" t="n">
-        <v>6.940037937728103</v>
+        <v>6.942005974260733</v>
       </c>
     </row>
     <row r="254">
@@ -10855,7 +10855,7 @@
         <v>7</v>
       </c>
       <c r="K254" t="n">
-        <v>6.93016237048678</v>
+        <v>6.930549545885073</v>
       </c>
     </row>
     <row r="255">
@@ -10896,7 +10896,7 @@
         <v>7</v>
       </c>
       <c r="K255" t="n">
-        <v>6.881720950445676</v>
+        <v>6.880799250615472</v>
       </c>
     </row>
     <row r="256">
@@ -10937,7 +10937,7 @@
         <v>7</v>
       </c>
       <c r="K256" t="n">
-        <v>6.887369828723834</v>
+        <v>6.888694006086773</v>
       </c>
     </row>
     <row r="257">
@@ -10978,7 +10978,7 @@
         <v>7</v>
       </c>
       <c r="K257" t="n">
-        <v>6.897370209718122</v>
+        <v>6.895701834256979</v>
       </c>
     </row>
     <row r="258">
@@ -11019,7 +11019,7 @@
         <v>7</v>
       </c>
       <c r="K258" t="n">
-        <v>7.019634701549224</v>
+        <v>7.018718702796285</v>
       </c>
     </row>
     <row r="259">
@@ -11060,7 +11060,7 @@
         <v>7</v>
       </c>
       <c r="K259" t="n">
-        <v>7.261734544884275</v>
+        <v>7.255915259470625</v>
       </c>
     </row>
     <row r="260">
@@ -11101,7 +11101,7 @@
         <v>7</v>
       </c>
       <c r="K260" t="n">
-        <v>7.337199573793328</v>
+        <v>7.335757145170267</v>
       </c>
     </row>
     <row r="261">
@@ -11142,7 +11142,7 @@
         <v>7</v>
       </c>
       <c r="K261" t="n">
-        <v>7.353648766155164</v>
+        <v>7.395306260371563</v>
       </c>
     </row>
     <row r="262">
@@ -11183,7 +11183,7 @@
         <v>7</v>
       </c>
       <c r="K262" t="n">
-        <v>7.697364158138308</v>
+        <v>7.684266951408063</v>
       </c>
     </row>
     <row r="263">
@@ -11224,7 +11224,7 @@
         <v>7</v>
       </c>
       <c r="K263" t="n">
-        <v>7.813713083694449</v>
+        <v>7.812445957380925</v>
       </c>
     </row>
     <row r="264">
@@ -11265,7 +11265,7 @@
         <v>7</v>
       </c>
       <c r="K264" t="n">
-        <v>7.852861725447755</v>
+        <v>7.852442855821411</v>
       </c>
     </row>
     <row r="265">
@@ -11306,7 +11306,7 @@
         <v>7</v>
       </c>
       <c r="K265" t="n">
-        <v>7.809475589085111</v>
+        <v>7.804790645072968</v>
       </c>
     </row>
     <row r="266">
@@ -11347,7 +11347,7 @@
         <v>7</v>
       </c>
       <c r="K266" t="n">
-        <v>7.801980325901026</v>
+        <v>7.804790645072968</v>
       </c>
     </row>
     <row r="267">
@@ -11388,7 +11388,7 @@
         <v>7</v>
       </c>
       <c r="K267" t="n">
-        <v>7.754980503365975</v>
+        <v>7.757289974892627</v>
       </c>
     </row>
     <row r="268">
@@ -11429,7 +11429,7 @@
         <v>7</v>
       </c>
       <c r="K268" t="n">
-        <v>7.754043892148252</v>
+        <v>7.753198775416064</v>
       </c>
     </row>
     <row r="269">
@@ -11470,7 +11470,7 @@
         <v>7</v>
       </c>
       <c r="K269" t="n">
-        <v>7.766742730517447</v>
+        <v>7.811319883900175</v>
       </c>
     </row>
     <row r="270">
@@ -11511,7 +11511,7 @@
         <v>7</v>
       </c>
       <c r="K270" t="n">
-        <v>7.905784414110376</v>
+        <v>7.896187374591876</v>
       </c>
     </row>
     <row r="271">
@@ -11552,7 +11552,7 @@
         <v>7</v>
       </c>
       <c r="K271" t="n">
-        <v>7.905784414110376</v>
+        <v>7.947065880865615</v>
       </c>
     </row>
     <row r="272">
@@ -11593,7 +11593,7 @@
         <v>7</v>
       </c>
       <c r="K272" t="n">
-        <v>8.091589868342119</v>
+        <v>8.091160802428435</v>
       </c>
     </row>
     <row r="273">
@@ -11634,7 +11634,7 @@
         <v>7</v>
       </c>
       <c r="K273" t="n">
-        <v>8.091589868342119</v>
+        <v>8.091160802428435</v>
       </c>
     </row>
     <row r="274">
@@ -11675,7 +11675,7 @@
         <v>7</v>
       </c>
       <c r="K274" t="n">
-        <v>8.094802967818806</v>
+        <v>8.094923772557038</v>
       </c>
     </row>
     <row r="275">
@@ -11716,7 +11716,7 @@
         <v>7</v>
       </c>
       <c r="K275" t="n">
-        <v>7.88378320299368</v>
+        <v>7.887845131643867</v>
       </c>
     </row>
     <row r="276">
@@ -11757,7 +11757,7 @@
         <v>7</v>
       </c>
       <c r="K276" t="n">
-        <v>7.88378320299368</v>
+        <v>7.887845131643867</v>
       </c>
     </row>
     <row r="277">
@@ -11798,7 +11798,7 @@
         <v>7</v>
       </c>
       <c r="K277" t="n">
-        <v>7.750076640136291</v>
+        <v>7.754767982644371</v>
       </c>
     </row>
     <row r="278">
@@ -11839,7 +11839,7 @@
         <v>7</v>
       </c>
       <c r="K278" t="n">
-        <v>7.615851548817426</v>
+        <v>7.620024938158743</v>
       </c>
     </row>
     <row r="279">
@@ -11880,7 +11880,7 @@
         <v>7</v>
       </c>
       <c r="K279" t="n">
-        <v>7.4976540749409</v>
+        <v>7.501313960902893</v>
       </c>
     </row>
     <row r="280">
@@ -11921,7 +11921,7 @@
         <v>7</v>
       </c>
       <c r="K280" t="n">
-        <v>7.399174672738896</v>
+        <v>7.385119377595603</v>
       </c>
     </row>
     <row r="281">
@@ -11962,7 +11962,7 @@
         <v>7</v>
       </c>
       <c r="K281" t="n">
-        <v>7.172019078035414</v>
+        <v>7.157354591734371</v>
       </c>
     </row>
     <row r="282">
@@ -12003,7 +12003,7 @@
         <v>7</v>
       </c>
       <c r="K282" t="n">
-        <v>7.022623340920935</v>
+        <v>7.024544672137996</v>
       </c>
     </row>
     <row r="283">
@@ -12044,7 +12044,7 @@
         <v>7</v>
       </c>
       <c r="K283" t="n">
-        <v>7.022623340920935</v>
+        <v>7.024544672137996</v>
       </c>
     </row>
     <row r="284">
@@ -12085,7 +12085,7 @@
         <v>7</v>
       </c>
       <c r="K284" t="n">
-        <v>6.949621456732038</v>
+        <v>6.958098631593606</v>
       </c>
     </row>
     <row r="285">
@@ -12126,7 +12126,7 @@
         <v>7</v>
       </c>
       <c r="K285" t="n">
-        <v>6.744780477562138</v>
+        <v>6.745824529699249</v>
       </c>
     </row>
     <row r="286">
@@ -12167,7 +12167,7 @@
         <v>7</v>
       </c>
       <c r="K286" t="n">
-        <v>6.716721062381463</v>
+        <v>6.711301953933487</v>
       </c>
     </row>
     <row r="287">
@@ -12208,7 +12208,7 @@
         <v>7</v>
       </c>
       <c r="K287" t="n">
-        <v>6.662865397376675</v>
+        <v>6.664070680251434</v>
       </c>
     </row>
     <row r="288">
@@ -12249,7 +12249,7 @@
         <v>7</v>
       </c>
       <c r="K288" t="n">
-        <v>6.633904050308234</v>
+        <v>6.628438016144022</v>
       </c>
     </row>
     <row r="289">
@@ -12290,7 +12290,7 @@
         <v>7</v>
       </c>
       <c r="K289" t="n">
-        <v>6.636489709097011</v>
+        <v>6.653153305337002</v>
       </c>
     </row>
     <row r="290">
@@ -12331,7 +12331,7 @@
         <v>7</v>
       </c>
       <c r="K290" t="n">
-        <v>6.811267640851021</v>
+        <v>6.806096181531817</v>
       </c>
     </row>
     <row r="291">
@@ -12372,7 +12372,7 @@
         <v>7</v>
       </c>
       <c r="K291" t="n">
-        <v>6.811267640851021</v>
+        <v>6.806096181531817</v>
       </c>
     </row>
     <row r="292">
@@ -12413,7 +12413,7 @@
         <v>7</v>
       </c>
       <c r="K292" t="n">
-        <v>6.811267640851021</v>
+        <v>6.806096181531817</v>
       </c>
     </row>
     <row r="293">
@@ -12454,7 +12454,7 @@
         <v>7</v>
       </c>
       <c r="K293" t="n">
-        <v>7.237652280391756</v>
+        <v>7.234413896642751</v>
       </c>
     </row>
     <row r="294">
@@ -12495,7 +12495,7 @@
         <v>7</v>
       </c>
       <c r="K294" t="n">
-        <v>7.370496241404817</v>
+        <v>7.436464405797164</v>
       </c>
     </row>
     <row r="295">
@@ -12536,7 +12536,7 @@
         <v>7</v>
       </c>
       <c r="K295" t="n">
-        <v>7.439838427456145</v>
+        <v>7.436464405797164</v>
       </c>
     </row>
     <row r="296">
@@ -12577,7 +12577,7 @@
         <v>7</v>
       </c>
       <c r="K296" t="n">
-        <v>7.476240368690293</v>
+        <v>7.459374670481116</v>
       </c>
     </row>
     <row r="297">
@@ -12618,7 +12618,7 @@
         <v>7</v>
       </c>
       <c r="K297" t="n">
-        <v>7.678188940940187</v>
+        <v>7.663399082393298</v>
       </c>
     </row>
     <row r="298">
@@ -12659,7 +12659,7 @@
         <v>7</v>
       </c>
       <c r="K298" t="n">
-        <v>7.733481435354341</v>
+        <v>7.730767181066641</v>
       </c>
     </row>
     <row r="299">
@@ -12700,7 +12700,7 @@
         <v>7</v>
       </c>
       <c r="K299" t="n">
-        <v>7.759006721757935</v>
+        <v>7.747134464325244</v>
       </c>
     </row>
     <row r="300">
@@ -12741,7 +12741,7 @@
         <v>7</v>
       </c>
       <c r="K300" t="n">
-        <v>7.804956245711396</v>
+        <v>7.802628451831043</v>
       </c>
     </row>
     <row r="301">
@@ -12782,7 +12782,7 @@
         <v>7</v>
       </c>
       <c r="K301" t="n">
-        <v>7.804956245711396</v>
+        <v>7.802628451831043</v>
       </c>
     </row>
     <row r="302">
@@ -12823,7 +12823,7 @@
         <v>7</v>
       </c>
       <c r="K302" t="n">
-        <v>7.848477482105796</v>
+        <v>7.851323757950896</v>
       </c>
     </row>
     <row r="303">
@@ -12864,7 +12864,7 @@
         <v>7</v>
       </c>
       <c r="K303" t="n">
-        <v>7.821414167292595</v>
+        <v>7.79576681565711</v>
       </c>
     </row>
     <row r="304">
@@ -12905,7 +12905,7 @@
         <v>7</v>
       </c>
       <c r="K304" t="n">
-        <v>7.821414167292595</v>
+        <v>7.79576681565711</v>
       </c>
     </row>
     <row r="305">
@@ -12946,7 +12946,7 @@
         <v>7</v>
       </c>
       <c r="K305" t="n">
-        <v>7.676128669843547</v>
+        <v>7.678471005022509</v>
       </c>
     </row>
     <row r="306">
@@ -12987,7 +12987,7 @@
         <v>7</v>
       </c>
       <c r="K306" t="n">
-        <v>7.607003620597352</v>
+        <v>7.609931305978408</v>
       </c>
     </row>
     <row r="307">
@@ -13028,7 +13028,7 @@
         <v>7</v>
       </c>
       <c r="K307" t="n">
-        <v>7.582199511561298</v>
+        <v>7.594227882409046</v>
       </c>
     </row>
     <row r="308">
@@ -13069,7 +13069,7 @@
         <v>7</v>
       </c>
       <c r="K308" t="n">
-        <v>7.513040273045318</v>
+        <v>7.522836802289743</v>
       </c>
     </row>
     <row r="309">
@@ -13110,7 +13110,7 @@
         <v>7</v>
       </c>
       <c r="K309" t="n">
-        <v>7.465403287105601</v>
+        <v>7.465481402965496</v>
       </c>
     </row>
     <row r="310">
@@ -13151,7 +13151,7 @@
         <v>7</v>
       </c>
       <c r="K310" t="n">
-        <v>7.381873541546802</v>
+        <v>7.384943791489403</v>
       </c>
     </row>
     <row r="311">
@@ -13192,7 +13192,7 @@
         <v>7</v>
       </c>
       <c r="K311" t="n">
-        <v>7.381873541546802</v>
+        <v>7.384943791489403</v>
       </c>
     </row>
     <row r="312">
@@ -13233,7 +13233,7 @@
         <v>7</v>
       </c>
       <c r="K312" t="n">
-        <v>7.34819049436848</v>
+        <v>7.36447856822238</v>
       </c>
     </row>
     <row r="313">
@@ -13274,7 +13274,7 @@
         <v>7</v>
       </c>
       <c r="K313" t="n">
-        <v>7.34819049436848</v>
+        <v>7.36447856822238</v>
       </c>
     </row>
     <row r="314">
@@ -13315,7 +13315,7 @@
         <v>7</v>
       </c>
       <c r="K314" t="n">
-        <v>7.153524269182269</v>
+        <v>7.156615059956872</v>
       </c>
     </row>
     <row r="315">
@@ -13356,7 +13356,7 @@
         <v>7</v>
       </c>
       <c r="K315" t="n">
-        <v>7.108084786034201</v>
+        <v>7.029810944938665</v>
       </c>
     </row>
     <row r="316">
@@ -13397,7 +13397,7 @@
         <v>7</v>
       </c>
       <c r="K316" t="n">
-        <v>7.026264001038359</v>
+        <v>7.029810944938665</v>
       </c>
     </row>
     <row r="317">
@@ -13438,7 +13438,7 @@
         <v>7</v>
       </c>
       <c r="K317" t="n">
-        <v>6.830589873021131</v>
+        <v>6.839844961015226</v>
       </c>
     </row>
     <row r="318">
@@ -13479,7 +13479,7 @@
         <v>7</v>
       </c>
       <c r="K318" t="n">
-        <v>6.830589873021131</v>
+        <v>6.839844961015226</v>
       </c>
     </row>
     <row r="319">
@@ -13520,7 +13520,7 @@
         <v>7</v>
       </c>
       <c r="K319" t="n">
-        <v>6.677771599728734</v>
+        <v>6.660299542150244</v>
       </c>
     </row>
     <row r="320">
@@ -13561,7 +13561,7 @@
         <v>7</v>
       </c>
       <c r="K320" t="n">
-        <v>6.618872689533801</v>
+        <v>6.594303538675203</v>
       </c>
     </row>
     <row r="321">
@@ -13602,7 +13602,7 @@
         <v>7</v>
       </c>
       <c r="K321" t="n">
-        <v>6.576829319118065</v>
+        <v>6.58434003546021</v>
       </c>
     </row>
     <row r="322">
@@ -13643,7 +13643,7 @@
         <v>7</v>
       </c>
       <c r="K322" t="n">
-        <v>6.548009539852067</v>
+        <v>6.549592541836081</v>
       </c>
     </row>
     <row r="323">
@@ -13684,7 +13684,7 @@
         <v>7</v>
       </c>
       <c r="K323" t="n">
-        <v>6.497439067214024</v>
+        <v>6.469510150933785</v>
       </c>
     </row>
     <row r="324">
@@ -13725,7 +13725,7 @@
         <v>7</v>
       </c>
       <c r="K324" t="n">
-        <v>6.453909886628229</v>
+        <v>6.460414444690698</v>
       </c>
     </row>
     <row r="325">
@@ -13766,7 +13766,7 @@
         <v>7</v>
       </c>
       <c r="K325" t="n">
-        <v>6.412272716443038</v>
+        <v>6.419938671774504</v>
       </c>
     </row>
     <row r="326">
@@ -13807,7 +13807,7 @@
         <v>7</v>
       </c>
       <c r="K326" t="n">
-        <v>6.26656824033005</v>
+        <v>6.268922249781057</v>
       </c>
     </row>
     <row r="327">
@@ -13848,7 +13848,7 @@
         <v>7</v>
       </c>
       <c r="K327" t="n">
-        <v>6.26656824033005</v>
+        <v>6.268922249781057</v>
       </c>
     </row>
     <row r="328">
@@ -13889,7 +13889,7 @@
         <v>7</v>
       </c>
       <c r="K328" t="n">
-        <v>6.179887083221361</v>
+        <v>6.190925879339379</v>
       </c>
     </row>
     <row r="329">
@@ -13930,7 +13930,7 @@
         <v>7</v>
       </c>
       <c r="K329" t="n">
-        <v>6.066013995221533</v>
+        <v>6.068611681953345</v>
       </c>
     </row>
     <row r="330">
@@ -13971,7 +13971,7 @@
         <v>7</v>
       </c>
       <c r="K330" t="n">
-        <v>6.041663888962099</v>
+        <v>6.053122122734557</v>
       </c>
     </row>
     <row r="331">
@@ -14012,7 +14012,7 @@
         <v>7</v>
       </c>
       <c r="K331" t="n">
-        <v>5.999590089565928</v>
+        <v>6.00209000715434</v>
       </c>
     </row>
     <row r="332">
@@ -14053,7 +14053,7 @@
         <v>7</v>
       </c>
       <c r="K332" t="n">
-        <v>5.937678631716218</v>
+        <v>5.926461158265312</v>
       </c>
     </row>
     <row r="333">
@@ -14094,7 +14094,7 @@
         <v>7</v>
       </c>
       <c r="K333" t="n">
-        <v>5.831710507891906</v>
+        <v>5.822374149868225</v>
       </c>
     </row>
     <row r="334">
@@ -14135,7 +14135,7 @@
         <v>7</v>
       </c>
       <c r="K334" t="n">
-        <v>5.789907504334945</v>
+        <v>5.791157578200315</v>
       </c>
     </row>
     <row r="335">
@@ -14176,7 +14176,7 @@
         <v>7</v>
       </c>
       <c r="K335" t="n">
-        <v>5.76138303069191</v>
+        <v>5.762324100490123</v>
       </c>
     </row>
     <row r="336">
@@ -14217,7 +14217,7 @@
         <v>7</v>
       </c>
       <c r="K336" t="n">
-        <v>5.739746166575894</v>
+        <v>5.743382176924778</v>
       </c>
     </row>
     <row r="337">
@@ -14258,7 +14258,7 @@
         <v>7</v>
       </c>
       <c r="K337" t="n">
-        <v>5.711796318421265</v>
+        <v>5.712773000595837</v>
       </c>
     </row>
     <row r="338">
@@ -14299,7 +14299,7 @@
         <v>7</v>
       </c>
       <c r="K338" t="n">
-        <v>5.681233299173138</v>
+        <v>5.682736709411799</v>
       </c>
     </row>
     <row r="339">
@@ -14340,7 +14340,7 @@
         <v>7</v>
       </c>
       <c r="K339" t="n">
-        <v>5.603248403126044</v>
+        <v>5.614247369059662</v>
       </c>
     </row>
     <row r="340">
@@ -14381,7 +14381,7 @@
         <v>7</v>
       </c>
       <c r="K340" t="n">
-        <v>5.603248403126044</v>
+        <v>5.614247369059662</v>
       </c>
     </row>
     <row r="341">
@@ -14422,7 +14422,7 @@
         <v>7</v>
       </c>
       <c r="K341" t="n">
-        <v>5.450425930637783</v>
+        <v>5.466218631771539</v>
       </c>
     </row>
     <row r="342">
@@ -14463,7 +14463,7 @@
         <v>7</v>
       </c>
       <c r="K342" t="n">
-        <v>5.295686149951442</v>
+        <v>5.305409229519007</v>
       </c>
     </row>
     <row r="343">
@@ -14504,7 +14504,7 @@
         <v>7</v>
       </c>
       <c r="K343" t="n">
-        <v>5.33125954182276</v>
+        <v>5.33604241965882</v>
       </c>
     </row>
     <row r="344">
@@ -14545,7 +14545,7 @@
         <v>7</v>
       </c>
       <c r="K344" t="n">
-        <v>5.366807301755229</v>
+        <v>5.35960892797343</v>
       </c>
     </row>
     <row r="345">
@@ -14586,7 +14586,7 @@
         <v>7</v>
       </c>
       <c r="K345" t="n">
-        <v>5.377034269525428</v>
+        <v>5.387142983451969</v>
       </c>
     </row>
     <row r="346">
@@ -14627,7 +14627,7 @@
         <v>7</v>
       </c>
       <c r="K346" t="n">
-        <v>5.377034269525428</v>
+        <v>5.40774612996696</v>
       </c>
     </row>
     <row r="347">
@@ -14668,7 +14668,7 @@
         <v>8</v>
       </c>
       <c r="K347" t="n">
-        <v>5.493321358906104</v>
+        <v>5.719426062454195</v>
       </c>
     </row>
     <row r="348">
@@ -14709,7 +14709,7 @@
         <v>8</v>
       </c>
       <c r="K348" t="n">
-        <v>5.921274757599261</v>
+        <v>5.88979808595527</v>
       </c>
     </row>
     <row r="349">
@@ -14750,7 +14750,7 @@
         <v>8</v>
       </c>
       <c r="K349" t="n">
-        <v>6.214917426600278</v>
+        <v>6.499296775633698</v>
       </c>
     </row>
     <row r="350">
@@ -14791,7 +14791,7 @@
         <v>8</v>
       </c>
       <c r="K350" t="n">
-        <v>6.570106431209725</v>
+        <v>6.824065675352355</v>
       </c>
     </row>
     <row r="351">
@@ -14832,7 +14832,7 @@
         <v>8</v>
       </c>
       <c r="K351" t="n">
-        <v>7.161156435596227</v>
+        <v>7.111700443114519</v>
       </c>
     </row>
     <row r="352">
@@ -14873,7 +14873,7 @@
         <v>8</v>
       </c>
       <c r="K352" t="n">
-        <v>7.389881756015782</v>
+        <v>7.350085768168607</v>
       </c>
     </row>
     <row r="353">
@@ -14914,7 +14914,7 @@
         <v>8</v>
       </c>
       <c r="K353" t="n">
-        <v>8.871109403480718</v>
+        <v>8.689328393647941</v>
       </c>
     </row>
     <row r="354">
@@ -14955,7 +14955,7 @@
         <v>8</v>
       </c>
       <c r="K354" t="n">
-        <v>8.871109403480718</v>
+        <v>8.689328393647941</v>
       </c>
     </row>
     <row r="355">
@@ -14996,7 +14996,7 @@
         <v>8</v>
       </c>
       <c r="K355" t="n">
-        <v>11.22661762434423</v>
+        <v>11.14082425553577</v>
       </c>
     </row>
     <row r="356">
@@ -15037,7 +15037,7 @@
         <v>8</v>
       </c>
       <c r="K356" t="n">
-        <v>14.81693596118864</v>
+        <v>14.46430815433131</v>
       </c>
     </row>
     <row r="357">
@@ -15078,7 +15078,7 @@
         <v>8</v>
       </c>
       <c r="K357" t="n">
-        <v>14.81693596118864</v>
+        <v>14.46430815433131</v>
       </c>
     </row>
     <row r="358">
@@ -15119,7 +15119,7 @@
         <v>8</v>
       </c>
       <c r="K358" t="n">
-        <v>14.81693596118864</v>
+        <v>14.46430815433131</v>
       </c>
     </row>
     <row r="359">
@@ -15160,7 +15160,7 @@
         <v>8</v>
       </c>
       <c r="K359" t="n">
-        <v>16.80728253259878</v>
+        <v>16.49806365172457</v>
       </c>
     </row>
     <row r="360">
@@ -15201,7 +15201,7 @@
         <v>8</v>
       </c>
       <c r="K360" t="n">
-        <v>18.27372197466615</v>
+        <v>18.54965030674553</v>
       </c>
     </row>
     <row r="361">
@@ -15242,7 +15242,7 @@
         <v>8</v>
       </c>
       <c r="K361" t="n">
-        <v>19.76153767635307</v>
+        <v>19.99802404300854</v>
       </c>
     </row>
     <row r="362">
@@ -15283,7 +15283,7 @@
         <v>10</v>
       </c>
       <c r="K362" t="n">
-        <v>20.11929080395721</v>
+        <v>19.99802404300854</v>
       </c>
     </row>
     <row r="363">
@@ -15324,7 +15324,7 @@
         <v>10</v>
       </c>
       <c r="K363" t="n">
-        <v>20.11929080395721</v>
+        <v>19.99802404300854</v>
       </c>
     </row>
     <row r="364">
@@ -15365,7 +15365,7 @@
         <v>10</v>
       </c>
       <c r="K364" t="n">
-        <v>2.976425565039631</v>
+        <v>2.890562760142826</v>
       </c>
     </row>
     <row r="365">
@@ -15406,7 +15406,7 @@
         <v>10</v>
       </c>
       <c r="K365" t="n">
-        <v>2.602999224493226</v>
+        <v>2.618256260295772</v>
       </c>
     </row>
     <row r="366">
@@ -15447,7 +15447,7 @@
         <v>10</v>
       </c>
       <c r="K366" t="n">
-        <v>2.55042407319046</v>
+        <v>2.555222335537648</v>
       </c>
     </row>
     <row r="367">
@@ -15488,7 +15488,7 @@
         <v>10</v>
       </c>
       <c r="K367" t="n">
-        <v>2.55042407319046</v>
+        <v>2.555222335537648</v>
       </c>
     </row>
     <row r="368">
@@ -15529,7 +15529,7 @@
         <v>10</v>
       </c>
       <c r="K368" t="n">
-        <v>2.531912405985697</v>
+        <v>2.526756350395762</v>
       </c>
     </row>
     <row r="369">
@@ -15570,7 +15570,7 @@
         <v>10</v>
       </c>
       <c r="K369" t="n">
-        <v>2.528268033285077</v>
+        <v>2.526756350395762</v>
       </c>
     </row>
     <row r="370">
@@ -15611,7 +15611,7 @@
         <v>10</v>
       </c>
       <c r="K370" t="n">
-        <v>2.770887838335311</v>
+        <v>2.748994540450275</v>
       </c>
     </row>
     <row r="371">
@@ -15652,7 +15652,7 @@
         <v>10</v>
       </c>
       <c r="K371" t="n">
-        <v>3.009218317493618</v>
+        <v>2.987275909084011</v>
       </c>
     </row>
     <row r="372">
@@ -15693,7 +15693,7 @@
         <v>10</v>
       </c>
       <c r="K372" t="n">
-        <v>3.161646690971776</v>
+        <v>3.125396482487877</v>
       </c>
     </row>
     <row r="373">
@@ -15734,7 +15734,7 @@
         <v>10</v>
       </c>
       <c r="K373" t="n">
-        <v>3.762428392332434</v>
+        <v>3.73058848590943</v>
       </c>
     </row>
     <row r="374">
@@ -15775,7 +15775,7 @@
         <v>10</v>
       </c>
       <c r="K374" t="n">
-        <v>3.905090460659248</v>
+        <v>4.000512462105006</v>
       </c>
     </row>
     <row r="375">
@@ -15816,7 +15816,7 @@
         <v>10</v>
       </c>
       <c r="K375" t="n">
-        <v>4.017938788579678</v>
+        <v>4.000512462105006</v>
       </c>
     </row>
     <row r="376">
@@ -15857,7 +15857,7 @@
         <v>10</v>
       </c>
       <c r="K376" t="n">
-        <v>4.113316328515028</v>
+        <v>4.121554898127651</v>
       </c>
     </row>
     <row r="377">
@@ -15898,7 +15898,7 @@
         <v>10</v>
       </c>
       <c r="K377" t="n">
-        <v>3.97313404997042</v>
+        <v>3.986061711991955</v>
       </c>
     </row>
     <row r="378">
@@ -15939,7 +15939,7 @@
         <v>10</v>
       </c>
       <c r="K378" t="n">
-        <v>3.97313404997042</v>
+        <v>3.986061711991955</v>
       </c>
     </row>
     <row r="379">
@@ -15980,7 +15980,7 @@
         <v>10</v>
       </c>
       <c r="K379" t="n">
-        <v>3.97313404997042</v>
+        <v>3.986061711991955</v>
       </c>
     </row>
     <row r="380">
@@ -16021,7 +16021,7 @@
         <v>10</v>
       </c>
       <c r="K380" t="n">
-        <v>3.970200544971989</v>
+        <v>3.968978457918732</v>
       </c>
     </row>
     <row r="381">
@@ -16062,7 +16062,7 @@
         <v>10</v>
       </c>
       <c r="K381" t="n">
-        <v>4.129830958773236</v>
+        <v>4.11289679849413</v>
       </c>
     </row>
     <row r="382">
@@ -16103,7 +16103,7 @@
         <v>10</v>
       </c>
       <c r="K382" t="n">
-        <v>4.297234429566859</v>
+        <v>4.281088838252236</v>
       </c>
     </row>
     <row r="383">
@@ -16144,7 +16144,7 @@
         <v>10</v>
       </c>
       <c r="K383" t="n">
-        <v>4.378232414852485</v>
+        <v>4.36092231738257</v>
       </c>
     </row>
     <row r="384">
@@ -16185,7 +16185,7 @@
         <v>10</v>
       </c>
       <c r="K384" t="n">
-        <v>4.664272341152899</v>
+        <v>4.653406797112262</v>
       </c>
     </row>
     <row r="385">
@@ -16226,7 +16226,7 @@
         <v>10</v>
       </c>
       <c r="K385" t="n">
-        <v>4.666792437424791</v>
+        <v>4.671486186976522</v>
       </c>
     </row>
     <row r="386">
@@ -16267,7 +16267,7 @@
         <v>10</v>
       </c>
       <c r="K386" t="n">
-        <v>4.550213848862613</v>
+        <v>4.485745583270655</v>
       </c>
     </row>
     <row r="387">
@@ -16308,7 +16308,7 @@
         <v>10</v>
       </c>
       <c r="K387" t="n">
-        <v>4.47006614391796</v>
+        <v>4.485745583270655</v>
       </c>
     </row>
     <row r="388">
@@ -16349,7 +16349,7 @@
         <v>10</v>
       </c>
       <c r="K388" t="n">
-        <v>4.392947759918394</v>
+        <v>4.40698861281099</v>
       </c>
     </row>
     <row r="389">
@@ -16390,7 +16390,7 @@
         <v>10</v>
       </c>
       <c r="K389" t="n">
-        <v>4.392947759918394</v>
+        <v>4.40698861281099</v>
       </c>
     </row>
     <row r="390">
@@ -16431,7 +16431,7 @@
         <v>10</v>
       </c>
       <c r="K390" t="n">
-        <v>4.320880271097467</v>
+        <v>4.337299705852458</v>
       </c>
     </row>
     <row r="391">
@@ -16472,7 +16472,7 @@
         <v>10</v>
       </c>
       <c r="K391" t="n">
-        <v>3.90760683201155</v>
+        <v>3.940196236666972</v>
       </c>
     </row>
     <row r="392">
@@ -16513,7 +16513,7 @@
         <v>10</v>
       </c>
       <c r="K392" t="n">
-        <v>3.743888594062842</v>
+        <v>3.776344999743937</v>
       </c>
     </row>
     <row r="393">
@@ -16554,7 +16554,7 @@
         <v>10</v>
       </c>
       <c r="K393" t="n">
-        <v>3.56721296422073</v>
+        <v>3.422317993263373</v>
       </c>
     </row>
     <row r="394">
@@ -16595,7 +16595,7 @@
         <v>10</v>
       </c>
       <c r="K394" t="n">
-        <v>3.386855757617883</v>
+        <v>3.242036931510134</v>
       </c>
     </row>
     <row r="395">
@@ -16636,7 +16636,7 @@
         <v>10</v>
       </c>
       <c r="K395" t="n">
-        <v>3.018629373635984</v>
+        <v>2.860148314247857</v>
       </c>
     </row>
     <row r="396">
@@ -16677,7 +16677,7 @@
         <v>10</v>
       </c>
       <c r="K396" t="n">
-        <v>2.824891837680386</v>
+        <v>2.860148314247857</v>
       </c>
     </row>
     <row r="397">
@@ -16718,7 +16718,7 @@
         <v>10</v>
       </c>
       <c r="K397" t="n">
-        <v>2.824891837680386</v>
+        <v>2.713015263528086</v>
       </c>
     </row>
     <row r="398">
@@ -16759,7 +16759,7 @@
         <v>10</v>
       </c>
       <c r="K398" t="n">
-        <v>2.667839308285985</v>
+        <v>2.670849987007665</v>
       </c>
     </row>
     <row r="399">
@@ -16800,7 +16800,7 @@
         <v>10</v>
       </c>
       <c r="K399" t="n">
-        <v>2.673965844792407</v>
+        <v>2.669722706389689</v>
       </c>
     </row>
     <row r="400">
@@ -16841,7 +16841,7 @@
         <v>10</v>
       </c>
       <c r="K400" t="n">
-        <v>3.143800527532143</v>
+        <v>3.326203765269775</v>
       </c>
     </row>
     <row r="401">
@@ -16882,7 +16882,7 @@
         <v>10</v>
       </c>
       <c r="K401" t="n">
-        <v>3.366430250316554</v>
+        <v>3.326203765269775</v>
       </c>
     </row>
     <row r="402">
@@ -16923,7 +16923,7 @@
         <v>10</v>
       </c>
       <c r="K402" t="n">
-        <v>3.384056756694928</v>
+        <v>3.26011632477451</v>
       </c>
     </row>
     <row r="403">
@@ -16964,7 +16964,7 @@
         <v>10</v>
       </c>
       <c r="K403" t="n">
-        <v>3.21960346128667</v>
+        <v>3.26011632477451</v>
       </c>
     </row>
     <row r="404">
@@ -17005,7 +17005,7 @@
         <v>10</v>
       </c>
       <c r="K404" t="n">
-        <v>3.017168231869399</v>
+        <v>3.05599473050298</v>
       </c>
     </row>
     <row r="405">
@@ -17046,7 +17046,7 @@
         <v>10</v>
       </c>
       <c r="K405" t="n">
-        <v>3.017168231869399</v>
+        <v>3.05599473050298</v>
       </c>
     </row>
     <row r="406">
@@ -17087,7 +17087,7 @@
         <v>10</v>
       </c>
       <c r="K406" t="n">
-        <v>2.858106800754163</v>
+        <v>2.763075838779973</v>
       </c>
     </row>
     <row r="407">
@@ -17128,7 +17128,7 @@
         <v>10</v>
       </c>
       <c r="K407" t="n">
-        <v>2.858106800754163</v>
+        <v>2.763075838779973</v>
       </c>
     </row>
     <row r="408">
@@ -17169,7 +17169,7 @@
         <v>10</v>
       </c>
       <c r="K408" t="n">
-        <v>2.736217122773753</v>
+        <v>2.763075838779973</v>
       </c>
     </row>
     <row r="409">
@@ -17210,7 +17210,7 @@
         <v>10</v>
       </c>
       <c r="K409" t="n">
-        <v>2.622508661205843</v>
+        <v>2.651708919582172</v>
       </c>
     </row>
     <row r="410">
@@ -17251,7 +17251,7 @@
         <v>10</v>
       </c>
       <c r="K410" t="n">
-        <v>2.287351934385399</v>
+        <v>2.292108379156169</v>
       </c>
     </row>
     <row r="411">
@@ -17292,7 +17292,7 @@
         <v>10</v>
       </c>
       <c r="K411" t="n">
-        <v>2.287351934385399</v>
+        <v>2.28019062393891</v>
       </c>
     </row>
     <row r="412">
@@ -17333,7 +17333,7 @@
         <v>10</v>
       </c>
       <c r="K412" t="n">
-        <v>2.287351934385399</v>
+        <v>2.28019062393891</v>
       </c>
     </row>
     <row r="413">
@@ -17374,7 +17374,7 @@
         <v>10</v>
       </c>
       <c r="K413" t="n">
-        <v>2.430876006537966</v>
+        <v>2.417378120521195</v>
       </c>
     </row>
     <row r="414">
@@ -17415,7 +17415,7 @@
         <v>10</v>
       </c>
       <c r="K414" t="n">
-        <v>2.596055770753158</v>
+        <v>2.578888369437198</v>
       </c>
     </row>
     <row r="415">
@@ -17456,7 +17456,7 @@
         <v>10</v>
       </c>
       <c r="K415" t="n">
-        <v>2.596055770753158</v>
+        <v>2.678056650615502</v>
       </c>
     </row>
     <row r="416">
@@ -17497,7 +17497,7 @@
         <v>10</v>
       </c>
       <c r="K416" t="n">
-        <v>2.942938467363699</v>
+        <v>2.925809834624575</v>
       </c>
     </row>
     <row r="417">
@@ -17538,7 +17538,7 @@
         <v>10</v>
       </c>
       <c r="K417" t="n">
-        <v>3.067116841005617</v>
+        <v>3.055684925331787</v>
       </c>
     </row>
     <row r="418">
@@ -17579,7 +17579,7 @@
         <v>10</v>
       </c>
       <c r="K418" t="n">
-        <v>3.114620831184824</v>
+        <v>3.105597098485911</v>
       </c>
     </row>
     <row r="419">
@@ -17620,7 +17620,7 @@
         <v>10</v>
       </c>
       <c r="K419" t="n">
-        <v>3.203273527675162</v>
+        <v>3.191478029921758</v>
       </c>
     </row>
     <row r="420">
@@ -17661,7 +17661,7 @@
         <v>10</v>
       </c>
       <c r="K420" t="n">
-        <v>3.203273527675162</v>
+        <v>3.191478029921758</v>
       </c>
     </row>
     <row r="421">
@@ -17702,7 +17702,7 @@
         <v>10</v>
       </c>
       <c r="K421" t="n">
-        <v>3.203273527675162</v>
+        <v>3.237701300146776</v>
       </c>
     </row>
     <row r="422">
@@ -17743,7 +17743,7 @@
         <v>10</v>
       </c>
       <c r="K422" t="n">
-        <v>3.214501229979133</v>
+        <v>3.192189336423588</v>
       </c>
     </row>
     <row r="423">
@@ -17784,7 +17784,7 @@
         <v>10</v>
       </c>
       <c r="K423" t="n">
-        <v>3.149096854251128</v>
+        <v>3.16035062008168</v>
       </c>
     </row>
     <row r="424">
@@ -17825,7 +17825,7 @@
         <v>10</v>
       </c>
       <c r="K424" t="n">
-        <v>3.149096854251128</v>
+        <v>3.16035062008168</v>
       </c>
     </row>
     <row r="425">
@@ -17866,7 +17866,7 @@
         <v>10</v>
       </c>
       <c r="K425" t="n">
-        <v>3.014936804889148</v>
+        <v>3.029282212725016</v>
       </c>
     </row>
     <row r="426">
@@ -17907,7 +17907,7 @@
         <v>10</v>
       </c>
       <c r="K426" t="n">
-        <v>3.014936804889148</v>
+        <v>3.029282212725016</v>
       </c>
     </row>
     <row r="427">
@@ -17948,7 +17948,7 @@
         <v>10</v>
       </c>
       <c r="K427" t="n">
-        <v>3.014936804889148</v>
+        <v>3.029282212725016</v>
       </c>
     </row>
     <row r="428">
@@ -17989,7 +17989,7 @@
         <v>10</v>
       </c>
       <c r="K428" t="n">
-        <v>2.937265027621964</v>
+        <v>2.877069096800672</v>
       </c>
     </row>
     <row r="429">
@@ -18030,7 +18030,7 @@
         <v>10</v>
       </c>
       <c r="K429" t="n">
-        <v>2.864297692938611</v>
+        <v>2.877069096800672</v>
       </c>
     </row>
     <row r="430">
@@ -18071,7 +18071,7 @@
         <v>10</v>
       </c>
       <c r="K430" t="n">
-        <v>2.864297692938611</v>
+        <v>2.877069096800672</v>
       </c>
     </row>
     <row r="431">
@@ -18112,7 +18112,7 @@
         <v>10</v>
       </c>
       <c r="K431" t="n">
-        <v>2.828990176169226</v>
+        <v>2.835271502704186</v>
       </c>
     </row>
     <row r="432">
@@ -18153,7 +18153,7 @@
         <v>10</v>
       </c>
       <c r="K432" t="n">
-        <v>2.794650880490688</v>
+        <v>2.802933030924317</v>
       </c>
     </row>
     <row r="433">
@@ -18194,7 +18194,7 @@
         <v>10</v>
       </c>
       <c r="K433" t="n">
-        <v>2.794650880490688</v>
+        <v>2.753429905215847</v>
       </c>
     </row>
     <row r="434">
@@ -18235,7 +18235,7 @@
         <v>10</v>
       </c>
       <c r="K434" t="n">
-        <v>2.538925870451505</v>
+        <v>2.557816689691518</v>
       </c>
     </row>
     <row r="435">
@@ -18276,7 +18276,7 @@
         <v>10</v>
       </c>
       <c r="K435" t="n">
-        <v>2.538925870451505</v>
+        <v>2.481133134091496</v>
       </c>
     </row>
     <row r="436">
@@ -18317,7 +18317,7 @@
         <v>10</v>
       </c>
       <c r="K436" t="n">
-        <v>2.468071202961318</v>
+        <v>2.481133134091496</v>
       </c>
     </row>
     <row r="437">
@@ -18358,7 +18358,7 @@
         <v>10</v>
       </c>
       <c r="K437" t="n">
-        <v>2.333992852968109</v>
+        <v>2.345101575297337</v>
       </c>
     </row>
     <row r="438">
@@ -18399,7 +18399,7 @@
         <v>10</v>
       </c>
       <c r="K438" t="n">
-        <v>2.276152280361631</v>
+        <v>2.292855928175527</v>
       </c>
     </row>
     <row r="439">
@@ -18440,7 +18440,7 @@
         <v>10</v>
       </c>
       <c r="K439" t="n">
-        <v>2.202283723152397</v>
+        <v>2.242317607060057</v>
       </c>
     </row>
     <row r="440">
@@ -18481,7 +18481,7 @@
         <v>10</v>
       </c>
       <c r="K440" t="n">
-        <v>2.202283723152397</v>
+        <v>2.242317607060057</v>
       </c>
     </row>
     <row r="441">
@@ -18522,7 +18522,7 @@
         <v>10</v>
       </c>
       <c r="K441" t="n">
-        <v>2.202283723152397</v>
+        <v>2.242317607060057</v>
       </c>
     </row>
     <row r="442">
@@ -18563,7 +18563,7 @@
         <v>10</v>
       </c>
       <c r="K442" t="n">
-        <v>2.404308670726555</v>
+        <v>2.443136484618107</v>
       </c>
     </row>
     <row r="443">
@@ -18604,7 +18604,7 @@
         <v>10</v>
       </c>
       <c r="K443" t="n">
-        <v>2.404308670726555</v>
+        <v>2.443136484618107</v>
       </c>
     </row>
     <row r="444">
@@ -18645,7 +18645,7 @@
         <v>10</v>
       </c>
       <c r="K444" t="n">
-        <v>3.059130585778412</v>
+        <v>2.928130832196366</v>
       </c>
     </row>
     <row r="445">
@@ -18686,7 +18686,7 @@
         <v>0</v>
       </c>
       <c r="K445" t="n">
-        <v>3.727313919145936</v>
+        <v>3.455790456892844</v>
       </c>
     </row>
   </sheetData>
